--- a/Decks/Alela.xlsx
+++ b/Decks/Alela.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F6AB15-9477-45CF-8628-9897C866F6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E55D247-2030-419E-A492-D94A768414BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{598AE8CA-FC72-432C-AF52-758C64378424}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{598AE8CA-FC72-432C-AF52-758C64378424}"/>
   </bookViews>
   <sheets>
     <sheet name="Alela" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="110">
   <si>
     <t>Função</t>
   </si>
@@ -191,9 +191,6 @@
     <t>Waterbender Ascension</t>
   </si>
   <si>
-    <t>Curiosity Crafter</t>
-  </si>
-  <si>
     <t>Wedding Ring</t>
   </si>
   <si>
@@ -338,9 +335,6 @@
     <t>Invasion of Tolvada</t>
   </si>
   <si>
-    <t>Bitterblossom</t>
-  </si>
-  <si>
     <t>Copy Enchantment</t>
   </si>
   <si>
@@ -357,6 +351,21 @@
   </si>
   <si>
     <t>Court of Vantress</t>
+  </si>
+  <si>
+    <t>Eiganjo Dynastorian // Replenish</t>
+  </si>
+  <si>
+    <t>Staff of the Storyteller</t>
+  </si>
+  <si>
+    <t>Monologue Tax</t>
+  </si>
+  <si>
+    <t>Faerie Mastermind</t>
+  </si>
+  <si>
+    <t>Artificer of Curiosity</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1111,7 @@
         <v>28</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1129,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1580,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1592,13 +1601,13 @@
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1622,13 +1631,13 @@
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1640,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1655,640 +1664,640 @@
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B60" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="D60" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C66" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="D72" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B86" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="D86" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C89" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D89" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="D94" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C95" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D95" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Alela.xlsx
+++ b/Decks/Alela.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E55D247-2030-419E-A492-D94A768414BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41B4E73-74D1-4A0F-8F81-D8CC4C678A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{598AE8CA-FC72-432C-AF52-758C64378424}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{598AE8CA-FC72-432C-AF52-758C64378424}"/>
   </bookViews>
   <sheets>
     <sheet name="Alela" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="106">
   <si>
     <t>Função</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Esper Panorama</t>
   </si>
   <si>
-    <t>Morphic Pool</t>
-  </si>
-  <si>
     <t>Westvale Abbey</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
     <t>Waterbender Ascension</t>
   </si>
   <si>
-    <t>Wedding Ring</t>
-  </si>
-  <si>
     <t>Enduring Curiosity</t>
   </si>
   <si>
@@ -218,9 +212,6 @@
     <t>Rest in Peace</t>
   </si>
   <si>
-    <t>Dispeller's Capsule</t>
-  </si>
-  <si>
     <t>Damping Sphere</t>
   </si>
   <si>
@@ -296,12 +287,6 @@
     <t>Intangible Virtue</t>
   </si>
   <si>
-    <t>Divine Visitation</t>
-  </si>
-  <si>
-    <t>Renewed Solidarity</t>
-  </si>
-  <si>
     <t>Archetype of Courage</t>
   </si>
   <si>
@@ -320,9 +305,6 @@
     <t>Court of Grace</t>
   </si>
   <si>
-    <t>The Immortal Sun</t>
-  </si>
-  <si>
     <t>Kambal, Profiteering Mayor</t>
   </si>
   <si>
@@ -366,6 +348,12 @@
   </si>
   <si>
     <t>Artificer of Curiosity</t>
+  </si>
+  <si>
+    <t>Scheming Silvertongue // Sign in Blood</t>
+  </si>
+  <si>
+    <t>Black Market Connections</t>
   </si>
 </sst>
 </file>
@@ -819,7 +807,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B67" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1090,13 +1078,13 @@
       </c>
       <c r="B21" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,13 +1093,13 @@
       </c>
       <c r="B22" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,13 +1108,13 @@
       </c>
       <c r="B23" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1138,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1153,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1168,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1183,10 +1171,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1198,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1209,14 +1197,14 @@
         <v>8</v>
       </c>
       <c r="B29" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C29&lt;&gt;D29</f>
         <v>0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1228,10 +1216,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1243,10 +1231,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1258,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1273,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1288,10 +1276,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1303,10 +1291,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1318,10 +1306,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1333,10 +1321,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1348,956 +1336,957 @@
         <v>0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="D39" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B41" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="D49" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F51"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C53&lt;&gt;D53</f>
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>52</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="E59" s="6"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>51</v>
+      </c>
+      <c r="B62" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B62" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="D62" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="D75" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>79</v>
+      </c>
+      <c r="B89" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B89" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="D89" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>87</v>
+      </c>
+      <c r="B100" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B100" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="D100" s="6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2307,7 +2296,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="notContainsText" priority="1" operator="notContains" id="{CE6A2588-D4DD-4F32-A1CD-1023AD1E040E}">
+          <x14:cfRule type="notContainsText" priority="2" operator="notContains" id="{CE6A2588-D4DD-4F32-A1CD-1023AD1E040E}">
             <xm:f>ISERROR(SEARCH(D2,C2))</xm:f>
             <xm:f>D2</xm:f>
             <x14:dxf>
